--- a/docs/templates/order-tracker-template.xlsx
+++ b/docs/templates/order-tracker-template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -437,9 +437,10 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -485,20 +486,25 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>ACR (USD per case)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Stock Reserved Qty</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Supplied Qty</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Supplied Date</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Invoice / Ref</t>
         </is>
